--- a/lucas/import_data/utility/observation/excel/provision_serial_nr.xlsx
+++ b/lucas/import_data/utility/observation/excel/provision_serial_nr.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,48 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t xml:space="preserve">provision_id__provision_name</t>
   </si>
   <si>
     <t xml:space="preserve">serial_nr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">xspectre npkphcth-s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x0001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x0002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x0003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x0004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foss ds2500 l</t>
-  </si>
-  <si>
-    <t xml:space="preserve">au</t>
-  </si>
-  <si>
-    <t xml:space="preserve">neospectra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoScanner_23040128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">neoscanner_auth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bruker invenio s ftir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foss micral</t>
   </si>
   <si>
     <t xml:space="preserve">foss xds rca</t>
@@ -147,7 +111,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -166,10 +130,6 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -192,37 +152,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -295,8 +255,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B372"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B363"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="33.55"/>
@@ -327,76 +287,31 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="B4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="B5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="B6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="B7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>11</v>
-      </c>
+      <c r="B8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="B9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="B10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="B11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="B12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="4"/>
@@ -1450,33 +1365,6 @@
     </row>
     <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B363" s="4"/>
-    </row>
-    <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B364" s="4"/>
-    </row>
-    <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B365" s="4"/>
-    </row>
-    <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B366" s="4"/>
-    </row>
-    <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B367" s="4"/>
-    </row>
-    <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B368" s="4"/>
-    </row>
-    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B369" s="4"/>
-    </row>
-    <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B370" s="4"/>
-    </row>
-    <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B371" s="4"/>
-    </row>
-    <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B372" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
